--- a/data_group/emmeans_intervalos_prec_table_final.xlsx
+++ b/data_group/emmeans_intervalos_prec_table_final.xlsx
@@ -458,31 +458,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>2363.47678362755</v>
+        <v>2361.90536791841</v>
       </c>
       <c r="D2" t="n">
-        <v>2626.88004648829</v>
+        <v>2626.38440601038</v>
       </c>
       <c r="E2" t="n">
-        <v>2100.4155477848</v>
+        <v>2099.85317346203</v>
       </c>
       <c r="F2" t="n">
-        <v>2270.23701627845</v>
+        <v>2330.56021337345</v>
       </c>
       <c r="G2" t="n">
-        <v>2535.49507941103</v>
+        <v>2587.47110836807</v>
       </c>
       <c r="H2" t="n">
-        <v>2031.96986000237</v>
+        <v>2081.81723079835</v>
       </c>
       <c r="I2" t="n">
-        <v>2456.71655097666</v>
+        <v>2393.25052246337</v>
       </c>
       <c r="J2" t="n">
-        <v>2718.26501356554</v>
+        <v>2665.29770365269</v>
       </c>
       <c r="K2" t="n">
-        <v>2168.86123556722</v>
+        <v>2117.88911612571</v>
       </c>
     </row>
     <row r="3">
@@ -493,31 +493,31 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>2229.37960167951</v>
+        <v>2228.95084566802</v>
       </c>
       <c r="D3" t="n">
-        <v>2136.1669600638</v>
+        <v>2136.34089652198</v>
       </c>
       <c r="E3" t="n">
-        <v>1997.75143549039</v>
+        <v>1997.44019800759</v>
       </c>
       <c r="F3" t="n">
-        <v>2136.13983432836</v>
+        <v>2212.94288698154</v>
       </c>
       <c r="G3" t="n">
-        <v>2044.7819929865</v>
+        <v>2126.49301459944</v>
       </c>
       <c r="H3" t="n">
-        <v>1929.30574770819</v>
+        <v>1992.47699538371</v>
       </c>
       <c r="I3" t="n">
-        <v>2322.61936903065</v>
+        <v>2244.95880435449</v>
       </c>
       <c r="J3" t="n">
-        <v>2227.55192714109</v>
+        <v>2146.18877844452</v>
       </c>
       <c r="K3" t="n">
-        <v>2066.1971232726</v>
+        <v>2002.40340063147</v>
       </c>
     </row>
     <row r="4">
@@ -528,31 +528,31 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>2252.14653541682</v>
+        <v>2252.82846542987</v>
       </c>
       <c r="D4" t="n">
-        <v>2168.15128552605</v>
+        <v>2167.33599524108</v>
       </c>
       <c r="E4" t="n">
-        <v>1979.39531170708</v>
+        <v>1977.77256180438</v>
       </c>
       <c r="F4" t="n">
-        <v>2158.90676806571</v>
+        <v>2245.46327983704</v>
       </c>
       <c r="G4" t="n">
-        <v>2076.76631844875</v>
+        <v>2152.96419714118</v>
       </c>
       <c r="H4" t="n">
-        <v>1910.94962392488</v>
+        <v>1969.81370276596</v>
       </c>
       <c r="I4" t="n">
-        <v>2345.38630276793</v>
+        <v>2260.1936510227</v>
       </c>
       <c r="J4" t="n">
-        <v>2259.53625260335</v>
+        <v>2181.70779334099</v>
       </c>
       <c r="K4" t="n">
-        <v>2047.84099948929</v>
+        <v>1985.73142084279</v>
       </c>
     </row>
     <row r="5">
@@ -563,31 +563,31 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>2289.72797284752</v>
+        <v>2296.49865991276</v>
       </c>
       <c r="D5" t="n">
-        <v>2205.46582342676</v>
+        <v>2201.04314533206</v>
       </c>
       <c r="E5" t="n">
-        <v>1941.2218335329</v>
+        <v>1949.19100685308</v>
       </c>
       <c r="F5" t="n">
-        <v>2193.9163806558</v>
+        <v>2275.16791594333</v>
       </c>
       <c r="G5" t="n">
-        <v>2111.39284017127</v>
+        <v>2163.26677944857</v>
       </c>
       <c r="H5" t="n">
-        <v>1871.25100476926</v>
+        <v>1934.44719665127</v>
       </c>
       <c r="I5" t="n">
-        <v>2385.53956503924</v>
+        <v>2317.82940388218</v>
       </c>
       <c r="J5" t="n">
-        <v>2299.53880668226</v>
+        <v>2238.81951121554</v>
       </c>
       <c r="K5" t="n">
-        <v>2011.19266229655</v>
+        <v>1963.93481705489</v>
       </c>
     </row>
     <row r="6">
@@ -598,31 +598,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>2395.94015531075</v>
+        <v>2394.99356727514</v>
       </c>
       <c r="D6" t="n">
-        <v>2572.52319244094</v>
+        <v>2572.24191816816</v>
       </c>
       <c r="E6" t="n">
-        <v>2103.56199822303</v>
+        <v>2103.21418967424</v>
       </c>
       <c r="F6" t="n">
-        <v>2302.70038796149</v>
+        <v>2364.32031598644</v>
       </c>
       <c r="G6" t="n">
-        <v>2481.13822536375</v>
+        <v>2539.11978097635</v>
       </c>
       <c r="H6" t="n">
-        <v>2035.11631044072</v>
+        <v>2085.9303641858</v>
       </c>
       <c r="I6" t="n">
-        <v>2489.17992266</v>
+        <v>2425.66681856384</v>
       </c>
       <c r="J6" t="n">
-        <v>2663.90815951813</v>
+        <v>2605.36405535996</v>
       </c>
       <c r="K6" t="n">
-        <v>2172.00768600533</v>
+        <v>2120.49801516268</v>
       </c>
     </row>
     <row r="7">
@@ -633,31 +633,31 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>2219.89716342746</v>
+        <v>2220.2289209526</v>
       </c>
       <c r="D7" t="n">
-        <v>2078.84184643685</v>
+        <v>2079.63131624716</v>
       </c>
       <c r="E7" t="n">
-        <v>2001.55978290173</v>
+        <v>2000.79548688961</v>
       </c>
       <c r="F7" t="n">
-        <v>2126.65739607635</v>
+        <v>2201.06000219575</v>
       </c>
       <c r="G7" t="n">
-        <v>1987.4568793596</v>
+        <v>2064.57693814305</v>
       </c>
       <c r="H7" t="n">
-        <v>1933.1140951195</v>
+        <v>1994.20868751205</v>
       </c>
       <c r="I7" t="n">
-        <v>2313.13693077858</v>
+        <v>2239.39783970945</v>
       </c>
       <c r="J7" t="n">
-        <v>2170.22681351411</v>
+        <v>2094.68569435127</v>
       </c>
       <c r="K7" t="n">
-        <v>2070.00547068396</v>
+        <v>2007.38228626717</v>
       </c>
     </row>
     <row r="8">
@@ -668,31 +668,31 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2246.39524132936</v>
+        <v>2246.49452504382</v>
       </c>
       <c r="D8" t="n">
-        <v>2141.39004261939</v>
+        <v>2138.66897174029</v>
       </c>
       <c r="E8" t="n">
-        <v>1981.42088760572</v>
+        <v>1981.21298674088</v>
       </c>
       <c r="F8" t="n">
-        <v>2153.15547397827</v>
+        <v>2242.65460676591</v>
       </c>
       <c r="G8" t="n">
-        <v>2050.00507554213</v>
+        <v>2118.01555886271</v>
       </c>
       <c r="H8" t="n">
-        <v>1912.97519982349</v>
+        <v>1976.92840658742</v>
       </c>
       <c r="I8" t="n">
-        <v>2339.63500868046</v>
+        <v>2250.33444332174</v>
       </c>
       <c r="J8" t="n">
-        <v>2232.77500969664</v>
+        <v>2159.32238461787</v>
       </c>
       <c r="K8" t="n">
-        <v>2049.86657538795</v>
+        <v>1985.49756689435</v>
       </c>
     </row>
     <row r="9">
@@ -703,31 +703,31 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>2276.73279183469</v>
+        <v>2277.31408082023</v>
       </c>
       <c r="D9" t="n">
-        <v>2221.96540420014</v>
+        <v>2219.92905786158</v>
       </c>
       <c r="E9" t="n">
-        <v>1930.20741096296</v>
+        <v>1938.99410508431</v>
       </c>
       <c r="F9" t="n">
-        <v>2180.92119964297</v>
+        <v>2258.05164765034</v>
       </c>
       <c r="G9" t="n">
-        <v>2127.89242094468</v>
+        <v>2189.40470942431</v>
       </c>
       <c r="H9" t="n">
-        <v>1860.23658219929</v>
+        <v>1923.33785240834</v>
       </c>
       <c r="I9" t="n">
-        <v>2372.5443840264</v>
+        <v>2296.57651399011</v>
       </c>
       <c r="J9" t="n">
-        <v>2316.03838745559</v>
+        <v>2250.45340629885</v>
       </c>
       <c r="K9" t="n">
-        <v>2000.17823972663</v>
+        <v>1954.65035776029</v>
       </c>
     </row>
     <row r="10">
@@ -738,31 +738,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>2416.06284108386</v>
+        <v>2415.70580619051</v>
       </c>
       <c r="D10" t="n">
-        <v>2528.8770914446</v>
+        <v>2528.7121304089</v>
       </c>
       <c r="E10" t="n">
-        <v>2097.99885867492</v>
+        <v>2097.97897139505</v>
       </c>
       <c r="F10" t="n">
-        <v>2322.82307373468</v>
+        <v>2385.53912551952</v>
       </c>
       <c r="G10" t="n">
-        <v>2437.49212436746</v>
+        <v>2500.12432807697</v>
       </c>
       <c r="H10" t="n">
-        <v>2029.55317089272</v>
+        <v>2081.51648681192</v>
       </c>
       <c r="I10" t="n">
-        <v>2509.30260843304</v>
+        <v>2445.8724868615</v>
       </c>
       <c r="J10" t="n">
-        <v>2620.26205852174</v>
+        <v>2557.29993274082</v>
       </c>
       <c r="K10" t="n">
-        <v>2166.44454645712</v>
+        <v>2114.44145597817</v>
       </c>
     </row>
     <row r="11">
@@ -773,31 +773,31 @@
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>2217.58552343058</v>
+        <v>2217.56646901064</v>
       </c>
       <c r="D11" t="n">
-        <v>2032.47274892286</v>
+        <v>2034.19988617435</v>
       </c>
       <c r="E11" t="n">
-        <v>1993.84126845279</v>
+        <v>1990.40438030747</v>
       </c>
       <c r="F11" t="n">
-        <v>2124.34575607951</v>
+        <v>2192.9719919748</v>
       </c>
       <c r="G11" t="n">
-        <v>1941.08778184543</v>
+        <v>2008.93655788811</v>
       </c>
       <c r="H11" t="n">
-        <v>1925.39558067056</v>
+        <v>1979.0245097193</v>
       </c>
       <c r="I11" t="n">
-        <v>2310.82529078165</v>
+        <v>2242.16094604648</v>
       </c>
       <c r="J11" t="n">
-        <v>2123.8577160003</v>
+        <v>2059.4632144606</v>
       </c>
       <c r="K11" t="n">
-        <v>2062.28695623503</v>
+        <v>2001.78425089564</v>
       </c>
     </row>
     <row r="12">
@@ -808,31 +808,31 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>2248.00297514708</v>
+        <v>2249.09454150637</v>
       </c>
       <c r="D12" t="n">
-        <v>2116.47961755598</v>
+        <v>2111.85809439259</v>
       </c>
       <c r="E12" t="n">
-        <v>1973.16013917114</v>
+        <v>1972.83351354645</v>
       </c>
       <c r="F12" t="n">
-        <v>2154.76320779604</v>
+        <v>2241.54055086349</v>
       </c>
       <c r="G12" t="n">
-        <v>2025.09465047855</v>
+        <v>2087.68959235069</v>
       </c>
       <c r="H12" t="n">
-        <v>1904.7144513889</v>
+        <v>1966.36009938859</v>
       </c>
       <c r="I12" t="n">
-        <v>2341.24274249812</v>
+        <v>2256.64853214926</v>
       </c>
       <c r="J12" t="n">
-        <v>2207.86458463342</v>
+        <v>2136.02659643449</v>
       </c>
       <c r="K12" t="n">
-        <v>2041.60582695337</v>
+        <v>1979.30692770432</v>
       </c>
     </row>
     <row r="13">
@@ -843,31 +843,31 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>2273.64624737001</v>
+        <v>2269.89902790244</v>
       </c>
       <c r="D13" t="n">
-        <v>2228.56745698735</v>
+        <v>2229.24098556708</v>
       </c>
       <c r="E13" t="n">
-        <v>1923.36105133666</v>
+        <v>1934.57992309297</v>
       </c>
       <c r="F13" t="n">
-        <v>2177.83465517834</v>
+        <v>2248.61178178643</v>
       </c>
       <c r="G13" t="n">
-        <v>2134.49447373174</v>
+        <v>2204.45178512144</v>
       </c>
       <c r="H13" t="n">
-        <v>1853.39022257299</v>
+        <v>1919.02935489732</v>
       </c>
       <c r="I13" t="n">
-        <v>2369.45783956168</v>
+        <v>2291.18627401844</v>
       </c>
       <c r="J13" t="n">
-        <v>2322.64044024296</v>
+        <v>2254.03018601273</v>
       </c>
       <c r="K13" t="n">
-        <v>1993.33188010033</v>
+        <v>1950.13049128862</v>
       </c>
     </row>
     <row r="14">
@@ -878,31 +878,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>2428.45488107962</v>
+        <v>2428.48591097126</v>
       </c>
       <c r="D14" t="n">
-        <v>2460.63225641516</v>
+        <v>2460.60505537115</v>
       </c>
       <c r="E14" t="n">
-        <v>2098.52297458507</v>
+        <v>2098.8274408839</v>
       </c>
       <c r="F14" t="n">
-        <v>2335.21511373054</v>
+        <v>2399.21027947214</v>
       </c>
       <c r="G14" t="n">
-        <v>2369.24728933817</v>
+        <v>2437.16902817006</v>
       </c>
       <c r="H14" t="n">
-        <v>2030.07728680282</v>
+        <v>2084.45332016024</v>
       </c>
       <c r="I14" t="n">
-        <v>2521.69464842871</v>
+        <v>2457.76154247038</v>
       </c>
       <c r="J14" t="n">
-        <v>2552.01722349214</v>
+        <v>2484.04108257225</v>
       </c>
       <c r="K14" t="n">
-        <v>2166.96866236732</v>
+        <v>2113.20156160755</v>
       </c>
     </row>
     <row r="15">
@@ -913,31 +913,31 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>2238.85509418235</v>
+        <v>2240.86820955406</v>
       </c>
       <c r="D15" t="n">
-        <v>2000.35616975318</v>
+        <v>2002.55155465503</v>
       </c>
       <c r="E15" t="n">
-        <v>1984.79657566225</v>
+        <v>1976.78214282232</v>
       </c>
       <c r="F15" t="n">
-        <v>2145.61532683129</v>
+        <v>2218.24446801473</v>
       </c>
       <c r="G15" t="n">
-        <v>1908.97120267576</v>
+        <v>1969.1901558439</v>
       </c>
       <c r="H15" t="n">
-        <v>1916.35088787999</v>
+        <v>1957.22056346234</v>
       </c>
       <c r="I15" t="n">
-        <v>2332.0948615334</v>
+        <v>2263.49195109338</v>
       </c>
       <c r="J15" t="n">
-        <v>2091.7411368306</v>
+        <v>2035.91295346616</v>
       </c>
       <c r="K15" t="n">
-        <v>2053.24226344452</v>
+        <v>1996.3437221823</v>
       </c>
     </row>
     <row r="16">
@@ -948,31 +948,31 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>2261.21585459726</v>
+        <v>2262.77553020828</v>
       </c>
       <c r="D16" t="n">
-        <v>2090.21462626672</v>
+        <v>2084.67299530849</v>
       </c>
       <c r="E16" t="n">
-        <v>1965.99476343286</v>
+        <v>1964.22913585016</v>
       </c>
       <c r="F16" t="n">
-        <v>2167.97608724622</v>
+        <v>2251.99081043684</v>
       </c>
       <c r="G16" t="n">
-        <v>1998.8296591893</v>
+        <v>2059.32604479423</v>
       </c>
       <c r="H16" t="n">
-        <v>1897.5490756506</v>
+        <v>1954.92331030303</v>
       </c>
       <c r="I16" t="n">
-        <v>2354.4556219483</v>
+        <v>2273.56024997973</v>
       </c>
       <c r="J16" t="n">
-        <v>2181.59959334415</v>
+        <v>2110.01994582274</v>
       </c>
       <c r="K16" t="n">
-        <v>2034.44045121513</v>
+        <v>1973.53496139729</v>
       </c>
     </row>
     <row r="17">
@@ -983,31 +983,31 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>2281.8198926428</v>
+        <v>2276.42341061253</v>
       </c>
       <c r="D17" t="n">
-        <v>2220.71982441247</v>
+        <v>2223.30028907996</v>
       </c>
       <c r="E17" t="n">
-        <v>1918.51078310929</v>
+        <v>1929.48066624572</v>
       </c>
       <c r="F17" t="n">
-        <v>2186.00830045114</v>
+        <v>2249.31835736482</v>
       </c>
       <c r="G17" t="n">
-        <v>2126.64684115686</v>
+        <v>2199.61898265617</v>
       </c>
       <c r="H17" t="n">
-        <v>1848.53995434559</v>
+        <v>1911.97055403947</v>
       </c>
       <c r="I17" t="n">
-        <v>2377.63148483446</v>
+        <v>2303.52846386024</v>
       </c>
       <c r="J17" t="n">
-        <v>2314.79280766807</v>
+        <v>2246.98159550374</v>
       </c>
       <c r="K17" t="n">
-        <v>1988.48161187299</v>
+        <v>1946.99077845197</v>
       </c>
     </row>
     <row r="18">
@@ -1018,31 +1018,31 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>2429.2026018064</v>
+        <v>2429.69185016143</v>
       </c>
       <c r="D18" t="n">
-        <v>2378.57488374903</v>
+        <v>2378.57442975983</v>
       </c>
       <c r="E18" t="n">
-        <v>2084.51652800882</v>
+        <v>2085.17388450896</v>
       </c>
       <c r="F18" t="n">
-        <v>2335.96283445736</v>
+        <v>2402.08028152183</v>
       </c>
       <c r="G18" t="n">
-        <v>2287.18991667197</v>
+        <v>2362.52024155557</v>
       </c>
       <c r="H18" t="n">
-        <v>2016.07084022672</v>
+        <v>2074.29041514341</v>
       </c>
       <c r="I18" t="n">
-        <v>2522.44236915544</v>
+        <v>2457.30341880103</v>
       </c>
       <c r="J18" t="n">
-        <v>2469.95985082609</v>
+        <v>2394.62861796408</v>
       </c>
       <c r="K18" t="n">
-        <v>2152.96221579092</v>
+        <v>2096.0573538745</v>
       </c>
     </row>
     <row r="19">
@@ -1053,31 +1053,31 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>2222.94447434593</v>
+        <v>2224.48878995989</v>
       </c>
       <c r="D19" t="n">
-        <v>1981.60217547657</v>
+        <v>1981.20112992348</v>
       </c>
       <c r="E19" t="n">
-        <v>1984.85210225192</v>
+        <v>1976.0745701891</v>
       </c>
       <c r="F19" t="n">
-        <v>2129.7047069949</v>
+        <v>2197.20942280273</v>
       </c>
       <c r="G19" t="n">
-        <v>1890.21720839919</v>
+        <v>1939.61989943544</v>
       </c>
       <c r="H19" t="n">
-        <v>1916.40641446965</v>
+        <v>1955.75031923231</v>
       </c>
       <c r="I19" t="n">
-        <v>2316.18424169696</v>
+        <v>2251.76815711705</v>
       </c>
       <c r="J19" t="n">
-        <v>2072.98714255396</v>
+        <v>2022.78236041151</v>
       </c>
       <c r="K19" t="n">
-        <v>2053.29779003418</v>
+        <v>1996.39882114588</v>
       </c>
     </row>
     <row r="20">
@@ -1088,31 +1088,31 @@
         <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>2267.46844809519</v>
+        <v>2273.34592664869</v>
       </c>
       <c r="D20" t="n">
-        <v>2062.56893668614</v>
+        <v>2058.09595644375</v>
       </c>
       <c r="E20" t="n">
-        <v>1957.14952175858</v>
+        <v>1954.18033670018</v>
       </c>
       <c r="F20" t="n">
-        <v>2174.22868074418</v>
+        <v>2258.66883689458</v>
       </c>
       <c r="G20" t="n">
-        <v>1971.18396960875</v>
+        <v>2034.20035623735</v>
       </c>
       <c r="H20" t="n">
-        <v>1888.70383397631</v>
+        <v>1940.0091343945</v>
       </c>
       <c r="I20" t="n">
-        <v>2360.70821544619</v>
+        <v>2288.02301640281</v>
       </c>
       <c r="J20" t="n">
-        <v>2153.95390376353</v>
+        <v>2081.99155665015</v>
       </c>
       <c r="K20" t="n">
-        <v>2025.59520954084</v>
+        <v>1968.35153900586</v>
       </c>
     </row>
     <row r="21">
@@ -1123,31 +1123,31 @@
         <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>2285.58649013637</v>
+        <v>2278.77510012726</v>
       </c>
       <c r="D21" t="n">
-        <v>2183.44614684873</v>
+        <v>2184.23857636374</v>
       </c>
       <c r="E21" t="n">
-        <v>1902.92838398475</v>
+        <v>1908.2160931355</v>
       </c>
       <c r="F21" t="n">
-        <v>2189.77489794475</v>
+        <v>2250.89175373995</v>
       </c>
       <c r="G21" t="n">
-        <v>2089.37316359316</v>
+        <v>2159.5204912901</v>
       </c>
       <c r="H21" t="n">
-        <v>1832.95755522105</v>
+        <v>1892.11357914278</v>
       </c>
       <c r="I21" t="n">
-        <v>2381.398082328</v>
+        <v>2306.65844651457</v>
       </c>
       <c r="J21" t="n">
-        <v>2277.51913010431</v>
+        <v>2208.95666143738</v>
       </c>
       <c r="K21" t="n">
-        <v>1972.89921274846</v>
+        <v>1924.31860712823</v>
       </c>
     </row>
     <row r="22">
@@ -1158,31 +1158,31 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>2425.92304434706</v>
+        <v>2426.53322366439</v>
       </c>
       <c r="D22" t="n">
-        <v>2325.37605196329</v>
+        <v>2325.41817639424</v>
       </c>
       <c r="E22" t="n">
-        <v>2079.77982393024</v>
+        <v>2079.79697704615</v>
       </c>
       <c r="F22" t="n">
-        <v>2332.6832769979</v>
+        <v>2400.17318055965</v>
       </c>
       <c r="G22" t="n">
-        <v>2233.99108488617</v>
+        <v>2311.2898604649</v>
       </c>
       <c r="H22" t="n">
-        <v>2011.33413614812</v>
+        <v>2071.9156839803</v>
       </c>
       <c r="I22" t="n">
-        <v>2519.16281169622</v>
+        <v>2452.89326676912</v>
       </c>
       <c r="J22" t="n">
-        <v>2416.76101904041</v>
+        <v>2339.54649232357</v>
       </c>
       <c r="K22" t="n">
-        <v>2148.22551171236</v>
+        <v>2087.67827011201</v>
       </c>
     </row>
     <row r="23">
@@ -1193,31 +1193,31 @@
         <v>13</v>
       </c>
       <c r="C23" t="n">
-        <v>2226.14352917908</v>
+        <v>2222.64472448883</v>
       </c>
       <c r="D23" t="n">
-        <v>1949.09809538553</v>
+        <v>1946.13103097303</v>
       </c>
       <c r="E23" t="n">
-        <v>1979.81906867927</v>
+        <v>1960.09475263574</v>
       </c>
       <c r="F23" t="n">
-        <v>2132.90376182796</v>
+        <v>2184.95716545564</v>
       </c>
       <c r="G23" t="n">
-        <v>1857.71312830814</v>
+        <v>1900.96489069524</v>
       </c>
       <c r="H23" t="n">
-        <v>1911.37338089702</v>
+        <v>1931.04748389206</v>
       </c>
       <c r="I23" t="n">
-        <v>2319.3832965302</v>
+        <v>2260.33228352203</v>
       </c>
       <c r="J23" t="n">
-        <v>2040.48306246293</v>
+        <v>1991.29717125082</v>
       </c>
       <c r="K23" t="n">
-        <v>2048.26475646152</v>
+        <v>1989.14202137941</v>
       </c>
     </row>
     <row r="24">
@@ -1228,31 +1228,31 @@
         <v>14</v>
       </c>
       <c r="C24" t="n">
-        <v>2284.94958418686</v>
+        <v>2290.9241287599</v>
       </c>
       <c r="D24" t="n">
-        <v>2039.75508514909</v>
+        <v>2034.94542263616</v>
       </c>
       <c r="E24" t="n">
-        <v>1960.90430875491</v>
+        <v>1957.6836407165</v>
       </c>
       <c r="F24" t="n">
-        <v>2191.70981683576</v>
+        <v>2273.55861272165</v>
       </c>
       <c r="G24" t="n">
-        <v>1948.37011807169</v>
+        <v>2008.5316904217</v>
       </c>
       <c r="H24" t="n">
-        <v>1892.45862097266</v>
+        <v>1942.65102233737</v>
       </c>
       <c r="I24" t="n">
-        <v>2378.18935153795</v>
+        <v>2308.28964479815</v>
       </c>
       <c r="J24" t="n">
-        <v>2131.14005222648</v>
+        <v>2061.35915485062</v>
       </c>
       <c r="K24" t="n">
-        <v>2029.34999653716</v>
+        <v>1972.71625909562</v>
       </c>
     </row>
     <row r="25">
@@ -1263,31 +1263,31 @@
         <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>2310.57071417099</v>
+        <v>2301.41294471573</v>
       </c>
       <c r="D25" t="n">
-        <v>2142.1534041029</v>
+        <v>2142.38353018304</v>
       </c>
       <c r="E25" t="n">
-        <v>1913.24942164403</v>
+        <v>1922.62921533047</v>
       </c>
       <c r="F25" t="n">
-        <v>2214.75912197929</v>
+        <v>2268.67425020389</v>
       </c>
       <c r="G25" t="n">
-        <v>2048.08042084732</v>
+        <v>2115.73590725788</v>
       </c>
       <c r="H25" t="n">
-        <v>1843.27859288034</v>
+        <v>1905.38972092884</v>
       </c>
       <c r="I25" t="n">
-        <v>2406.3823063627</v>
+        <v>2334.15163922757</v>
       </c>
       <c r="J25" t="n">
-        <v>2236.22638735848</v>
+        <v>2169.03115310819</v>
       </c>
       <c r="K25" t="n">
-        <v>1983.22025040771</v>
+        <v>1939.86870973211</v>
       </c>
     </row>
     <row r="26">
@@ -1298,31 +1298,31 @@
         <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>2432.65735031357</v>
+        <v>2433.14610089361</v>
       </c>
       <c r="D26" t="n">
-        <v>2338.90772084839</v>
+        <v>2338.90941772459</v>
       </c>
       <c r="E26" t="n">
-        <v>2091.47363557756</v>
+        <v>2091.46267585095</v>
       </c>
       <c r="F26" t="n">
-        <v>2339.41758296435</v>
+        <v>2405.70570495721</v>
       </c>
       <c r="G26" t="n">
-        <v>2247.52275377123</v>
+        <v>2321.06535393424</v>
       </c>
       <c r="H26" t="n">
-        <v>2023.02794779531</v>
+        <v>2082.86831000091</v>
       </c>
       <c r="I26" t="n">
-        <v>2525.89711766279</v>
+        <v>2460.58649683002</v>
       </c>
       <c r="J26" t="n">
-        <v>2430.29268792555</v>
+        <v>2356.75348151495</v>
       </c>
       <c r="K26" t="n">
-        <v>2159.9193233598</v>
+        <v>2100.05704170099</v>
       </c>
     </row>
     <row r="27">
@@ -1333,31 +1333,31 @@
         <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>2229.30836127015</v>
+        <v>2240.3683042395</v>
       </c>
       <c r="D27" t="n">
-        <v>1946.84418970834</v>
+        <v>1942.0094893956</v>
       </c>
       <c r="E27" t="n">
-        <v>1975.20790803316</v>
+        <v>1957.78357101357</v>
       </c>
       <c r="F27" t="n">
-        <v>2136.06859391912</v>
+        <v>2209.04701093051</v>
       </c>
       <c r="G27" t="n">
-        <v>1855.45922263093</v>
+        <v>1894.694965582</v>
       </c>
       <c r="H27" t="n">
-        <v>1906.76222025078</v>
+        <v>1926.98653293982</v>
       </c>
       <c r="I27" t="n">
-        <v>2322.54812862117</v>
+        <v>2271.68959754848</v>
       </c>
       <c r="J27" t="n">
-        <v>2038.22915678576</v>
+        <v>1989.3240132092</v>
       </c>
       <c r="K27" t="n">
-        <v>2043.65359581553</v>
+        <v>1988.58060908733</v>
       </c>
     </row>
     <row r="28">
@@ -1368,31 +1368,31 @@
         <v>14</v>
       </c>
       <c r="C28" t="n">
-        <v>2333.04029316817</v>
+        <v>2339.75592214177</v>
       </c>
       <c r="D28" t="n">
-        <v>2037.11393451733</v>
+        <v>2034.78299760953</v>
       </c>
       <c r="E28" t="n">
-        <v>1934.99752721403</v>
+        <v>1929.84121499638</v>
       </c>
       <c r="F28" t="n">
-        <v>2239.80052581716</v>
+        <v>2315.13491091939</v>
       </c>
       <c r="G28" t="n">
-        <v>1945.72896743991</v>
+        <v>2009.74077433729</v>
       </c>
       <c r="H28" t="n">
-        <v>1866.55183943166</v>
+        <v>1913.8788584582</v>
       </c>
       <c r="I28" t="n">
-        <v>2426.28006051918</v>
+        <v>2364.37693336414</v>
       </c>
       <c r="J28" t="n">
-        <v>2128.49890159474</v>
+        <v>2059.82522088177</v>
       </c>
       <c r="K28" t="n">
-        <v>2003.4432149964</v>
+        <v>1945.80357153455</v>
       </c>
     </row>
     <row r="29">
@@ -1403,31 +1403,31 @@
         <v>15</v>
       </c>
       <c r="C29" t="n">
-        <v>2335.23528197239</v>
+        <v>2331.08416902997</v>
       </c>
       <c r="D29" t="n">
-        <v>2107.55442682852</v>
+        <v>2107.03341438464</v>
       </c>
       <c r="E29" t="n">
-        <v>1888.70014230584</v>
+        <v>1897.48922450284</v>
       </c>
       <c r="F29" t="n">
-        <v>2239.42368978076</v>
+        <v>2297.13509277855</v>
       </c>
       <c r="G29" t="n">
-        <v>2013.48144357292</v>
+        <v>2081.70600100653</v>
       </c>
       <c r="H29" t="n">
-        <v>1818.72931354204</v>
+        <v>1875.42339210644</v>
       </c>
       <c r="I29" t="n">
-        <v>2431.04687416403</v>
+        <v>2365.03324528139</v>
       </c>
       <c r="J29" t="n">
-        <v>2201.62741008411</v>
+        <v>2132.36082776275</v>
       </c>
       <c r="K29" t="n">
-        <v>1958.67097106964</v>
+        <v>1919.55505689923</v>
       </c>
     </row>
     <row r="30">
@@ -1438,31 +1438,31 @@
         <v>12</v>
       </c>
       <c r="C30" t="n">
-        <v>2439.78885429482</v>
+        <v>2440.24167893167</v>
       </c>
       <c r="D30" t="n">
-        <v>2348.77448680818</v>
+        <v>2348.63536708625</v>
       </c>
       <c r="E30" t="n">
-        <v>2099.80295449971</v>
+        <v>2099.69822253384</v>
       </c>
       <c r="F30" t="n">
-        <v>2346.54908694572</v>
+        <v>2412.14989683353</v>
       </c>
       <c r="G30" t="n">
-        <v>2257.38951973106</v>
+        <v>2326.23941394577</v>
       </c>
       <c r="H30" t="n">
-        <v>2031.3572667175</v>
+        <v>2090.50335939373</v>
       </c>
       <c r="I30" t="n">
-        <v>2533.02862164392</v>
+        <v>2468.33346102981</v>
       </c>
       <c r="J30" t="n">
-        <v>2440.15945388531</v>
+        <v>2371.03132022673</v>
       </c>
       <c r="K30" t="n">
-        <v>2168.24864228192</v>
+        <v>2108.89308567395</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1473,31 @@
         <v>13</v>
       </c>
       <c r="C31" t="n">
-        <v>2222.56419016753</v>
+        <v>2218.98021583521</v>
       </c>
       <c r="D31" t="n">
-        <v>1919.83559483248</v>
+        <v>1912.47126904352</v>
       </c>
       <c r="E31" t="n">
-        <v>1969.31630482658</v>
+        <v>1948.80243317224</v>
       </c>
       <c r="F31" t="n">
-        <v>2129.32442281644</v>
+        <v>2170.52340026774</v>
       </c>
       <c r="G31" t="n">
-        <v>1828.45062775504</v>
+        <v>1858.28659180976</v>
       </c>
       <c r="H31" t="n">
-        <v>1900.87061704425</v>
+        <v>1916.40004785232</v>
       </c>
       <c r="I31" t="n">
-        <v>2315.80395751863</v>
+        <v>2267.43703140269</v>
       </c>
       <c r="J31" t="n">
-        <v>2011.22056190991</v>
+        <v>1966.65594627728</v>
       </c>
       <c r="K31" t="n">
-        <v>2037.7619926089</v>
+        <v>1981.20481849217</v>
       </c>
     </row>
     <row r="32">
@@ -1508,31 +1508,31 @@
         <v>14</v>
       </c>
       <c r="C32" t="n">
-        <v>2301.90667497087</v>
+        <v>2326.25978804308</v>
       </c>
       <c r="D32" t="n">
-        <v>2025.78475088582</v>
+        <v>2022.52117650431</v>
       </c>
       <c r="E32" t="n">
-        <v>1931.30741112514</v>
+        <v>1928.60492224684</v>
       </c>
       <c r="F32" t="n">
-        <v>2208.6669076198</v>
+        <v>2291.20090158149</v>
       </c>
       <c r="G32" t="n">
-        <v>1934.39978380838</v>
+        <v>1993.7757863211</v>
       </c>
       <c r="H32" t="n">
-        <v>1862.86172334282</v>
+        <v>1912.17010765589</v>
       </c>
       <c r="I32" t="n">
-        <v>2395.14644232193</v>
+        <v>2361.31867450466</v>
       </c>
       <c r="J32" t="n">
-        <v>2117.16971796326</v>
+        <v>2051.26656668753</v>
       </c>
       <c r="K32" t="n">
-        <v>1999.75309890746</v>
+        <v>1945.03973683779</v>
       </c>
     </row>
     <row r="33">
@@ -1543,31 +1543,31 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>2358.69639697767</v>
+        <v>2347.80446966586</v>
       </c>
       <c r="D33" t="n">
-        <v>2089.94686695762</v>
+        <v>2090.67793243159</v>
       </c>
       <c r="E33" t="n">
-        <v>1883.7427849482</v>
+        <v>1885.19490685745</v>
       </c>
       <c r="F33" t="n">
-        <v>2262.88480478598</v>
+        <v>2307.91628666997</v>
       </c>
       <c r="G33" t="n">
-        <v>1995.87388370201</v>
+        <v>2058.75179330791</v>
       </c>
       <c r="H33" t="n">
-        <v>1813.77195618445</v>
+        <v>1857.04311717387</v>
       </c>
       <c r="I33" t="n">
-        <v>2454.50798916936</v>
+        <v>2387.69265266174</v>
       </c>
       <c r="J33" t="n">
-        <v>2184.01985021323</v>
+        <v>2122.60407155527</v>
       </c>
       <c r="K33" t="n">
-        <v>1953.71361371196</v>
+        <v>1913.34669654102</v>
       </c>
     </row>
     <row r="34">
@@ -1578,31 +1578,31 @@
         <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>2442.71573430648</v>
+        <v>2443.09419209583</v>
       </c>
       <c r="D34" t="n">
-        <v>2365.37259481641</v>
+        <v>2364.91531520841</v>
       </c>
       <c r="E34" t="n">
-        <v>2111.12289438676</v>
+        <v>2110.88442786224</v>
       </c>
       <c r="F34" t="n">
-        <v>2349.47596695753</v>
+        <v>2413.88084537609</v>
       </c>
       <c r="G34" t="n">
-        <v>2273.98762773935</v>
+        <v>2333.8001517889</v>
       </c>
       <c r="H34" t="n">
-        <v>2042.67720660469</v>
+        <v>2100.84743794448</v>
       </c>
       <c r="I34" t="n">
-        <v>2535.95550165542</v>
+        <v>2472.30753881556</v>
       </c>
       <c r="J34" t="n">
-        <v>2456.75756189346</v>
+        <v>2396.03047862791</v>
       </c>
       <c r="K34" t="n">
-        <v>2179.56858216883</v>
+        <v>2120.92141778</v>
       </c>
     </row>
     <row r="35">
@@ -1613,31 +1613,31 @@
         <v>13</v>
       </c>
       <c r="C35" t="n">
-        <v>2205.05799857304</v>
+        <v>2225.89270719642</v>
       </c>
       <c r="D35" t="n">
-        <v>1924.02236397875</v>
+        <v>1911.54867808412</v>
       </c>
       <c r="E35" t="n">
-        <v>1972.55675906088</v>
+        <v>1944.02685554953</v>
       </c>
       <c r="F35" t="n">
-        <v>2111.27858565126</v>
+        <v>2167.04278926632</v>
       </c>
       <c r="G35" t="n">
-        <v>1832.63739690136</v>
+        <v>1852.21853885138</v>
       </c>
       <c r="H35" t="n">
-        <v>1904.11107127858</v>
+        <v>1904.66397378829</v>
       </c>
       <c r="I35" t="n">
-        <v>2298.83741149481</v>
+        <v>2284.74262512653</v>
       </c>
       <c r="J35" t="n">
-        <v>2015.40733105614</v>
+        <v>1970.87881731687</v>
       </c>
       <c r="K35" t="n">
-        <v>2041.00244684319</v>
+        <v>1983.38973731078</v>
       </c>
     </row>
     <row r="36">
@@ -1648,31 +1648,31 @@
         <v>14</v>
       </c>
       <c r="C36" t="n">
-        <v>2332.38225643261</v>
+        <v>2368.05263807118</v>
       </c>
       <c r="D36" t="n">
-        <v>2040.56851895921</v>
+        <v>2034.55178585614</v>
       </c>
       <c r="E36" t="n">
-        <v>1935.19651233191</v>
+        <v>1926.85788415542</v>
       </c>
       <c r="F36" t="n">
-        <v>2239.14248908151</v>
+        <v>2336.07461457874</v>
       </c>
       <c r="G36" t="n">
-        <v>1949.18355188182</v>
+        <v>1995.90122045642</v>
       </c>
       <c r="H36" t="n">
-        <v>1866.7508245496</v>
+        <v>1908.61224871987</v>
       </c>
       <c r="I36" t="n">
-        <v>2425.62202378371</v>
+        <v>2400.03066156363</v>
       </c>
       <c r="J36" t="n">
-        <v>2131.9534860366</v>
+        <v>2073.20235125586</v>
       </c>
       <c r="K36" t="n">
-        <v>2003.64220011421</v>
+        <v>1945.10351959098</v>
       </c>
     </row>
     <row r="37">
@@ -1683,31 +1683,31 @@
         <v>15</v>
       </c>
       <c r="C37" t="n">
-        <v>2344.60566194958</v>
+        <v>2345.19546741415</v>
       </c>
       <c r="D37" t="n">
-        <v>2085.87652703463</v>
+        <v>2089.88528541988</v>
       </c>
       <c r="E37" t="n">
-        <v>1884.41752135971</v>
+        <v>1893.33444750761</v>
       </c>
       <c r="F37" t="n">
-        <v>2248.79406975786</v>
+        <v>2307.9691519358</v>
       </c>
       <c r="G37" t="n">
-        <v>1991.80354377905</v>
+        <v>2057.564223117</v>
       </c>
       <c r="H37" t="n">
-        <v>1814.44669259598</v>
+        <v>1861.96425645848</v>
       </c>
       <c r="I37" t="n">
-        <v>2440.41725414129</v>
+        <v>2382.42178289251</v>
       </c>
       <c r="J37" t="n">
-        <v>2179.9495102902</v>
+        <v>2122.20634772276</v>
       </c>
       <c r="K37" t="n">
-        <v>1954.38835012345</v>
+        <v>1924.70463855673</v>
       </c>
     </row>
     <row r="38">
@@ -1718,31 +1718,31 @@
         <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>2400.07333749576</v>
+        <v>2399.8734957251</v>
       </c>
       <c r="D38" t="n">
-        <v>2263.17197260983</v>
+        <v>2262.95726662889</v>
       </c>
       <c r="E38" t="n">
-        <v>2180.81622361863</v>
+        <v>2180.20468370441</v>
       </c>
       <c r="F38" t="n">
-        <v>2306.83357014655</v>
+        <v>2376.40711487271</v>
       </c>
       <c r="G38" t="n">
-        <v>2171.787005533</v>
+        <v>2215.61621104628</v>
       </c>
       <c r="H38" t="n">
-        <v>2112.37053583641</v>
+        <v>2162.11857513526</v>
       </c>
       <c r="I38" t="n">
-        <v>2493.31310484497</v>
+        <v>2423.33987657748</v>
       </c>
       <c r="J38" t="n">
-        <v>2354.55693968666</v>
+        <v>2310.29832221151</v>
       </c>
       <c r="K38" t="n">
-        <v>2249.26191140085</v>
+        <v>2198.29079227356</v>
       </c>
     </row>
     <row r="39">
@@ -1753,31 +1753,31 @@
         <v>13</v>
       </c>
       <c r="C39" t="n">
-        <v>2260.53280218538</v>
+        <v>2291.36392507921</v>
       </c>
       <c r="D39" t="n">
-        <v>1935.59618971211</v>
+        <v>1929.50261834458</v>
       </c>
       <c r="E39" t="n">
-        <v>1971.06626087606</v>
+        <v>1928.55580810532</v>
       </c>
       <c r="F39" t="n">
-        <v>2165.24560136572</v>
+        <v>2193.7905181107</v>
       </c>
       <c r="G39" t="n">
-        <v>1844.2112226346</v>
+        <v>1858.45280707348</v>
       </c>
       <c r="H39" t="n">
-        <v>1902.62057309375</v>
+        <v>1864.31246425099</v>
       </c>
       <c r="I39" t="n">
-        <v>2355.82000300504</v>
+        <v>2388.93733204771</v>
       </c>
       <c r="J39" t="n">
-        <v>2026.98115678961</v>
+        <v>2000.55242961567</v>
       </c>
       <c r="K39" t="n">
-        <v>2039.51194865837</v>
+        <v>1992.79915195966</v>
       </c>
     </row>
     <row r="40">
@@ -1788,31 +1788,31 @@
         <v>14</v>
       </c>
       <c r="C40" t="n">
-        <v>2359.46193910247</v>
+        <v>2397.53851826618</v>
       </c>
       <c r="D40" t="n">
-        <v>2063.23463960615</v>
+        <v>2058.31752088661</v>
       </c>
       <c r="E40" t="n">
-        <v>1917.56857900478</v>
+        <v>1904.04616338004</v>
       </c>
       <c r="F40" t="n">
-        <v>2266.22217175135</v>
+        <v>2343.11776400416</v>
       </c>
       <c r="G40" t="n">
-        <v>1971.84967252864</v>
+        <v>2020.81396314074</v>
       </c>
       <c r="H40" t="n">
-        <v>1849.12289122247</v>
+        <v>1870.70853260027</v>
       </c>
       <c r="I40" t="n">
-        <v>2452.70170645358</v>
+        <v>2451.9592725282</v>
       </c>
       <c r="J40" t="n">
-        <v>2154.61960668365</v>
+        <v>2095.82107863249</v>
       </c>
       <c r="K40" t="n">
-        <v>1986.01426678709</v>
+        <v>1937.3837941598</v>
       </c>
     </row>
     <row r="41">
@@ -1823,31 +1823,31 @@
         <v>15</v>
       </c>
       <c r="C41" t="n">
-        <v>2435.70851792257</v>
+        <v>2430.24995921455</v>
       </c>
       <c r="D41" t="n">
-        <v>2127.41803125595</v>
+        <v>2138.91284729082</v>
       </c>
       <c r="E41" t="n">
-        <v>1900.93287146909</v>
+        <v>1914.22587690175</v>
       </c>
       <c r="F41" t="n">
-        <v>2339.89692573084</v>
+        <v>2390.30360009134</v>
       </c>
       <c r="G41" t="n">
-        <v>2033.34504800027</v>
+        <v>2093.96572723502</v>
       </c>
       <c r="H41" t="n">
-        <v>1830.96204270534</v>
+        <v>1879.25082410211</v>
       </c>
       <c r="I41" t="n">
-        <v>2531.52011011429</v>
+        <v>2470.19631833775</v>
       </c>
       <c r="J41" t="n">
-        <v>2221.49101451163</v>
+        <v>2183.85996734663</v>
       </c>
       <c r="K41" t="n">
-        <v>1970.90370023283</v>
+        <v>1949.2009297014</v>
       </c>
     </row>
   </sheetData>
